--- a/NuevaData/Presentacion/Investigacion/FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE/b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Inteligencia de negocios.xlsx
+++ b/NuevaData/Presentacion/Investigacion/FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE/b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Inteligencia de negocios.xlsx
@@ -2586,25 +2586,57 @@
       <c r="J34" s="50"/>
     </row>
     <row r="35" spans="1:10" s="23" customFormat="1">
-      <c r="A35" s="72"/>
+      <c r="A35" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comprende la inteligencia de negocios como metodología de soporte a la toma de decisiones.</t>
+        </is>
+      </c>
       <c r="B35" s="73"/>
-      <c r="C35" s="78"/>
+      <c r="C35" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Comprender</t>
+        </is>
+      </c>
       <c r="D35" s="43"/>
       <c r="E35" s="43"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="79"/>
+      <c r="F35" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA01</t>
+        </is>
+      </c>
+      <c r="G35" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Explicar el concepto, los beneficios y los usuarios de la inteligencia de negocios y su papel en el soporte a la toma de decisiones organizacionales.</t>
+        </is>
+      </c>
       <c r="H35" s="80"/>
       <c r="I35" s="81"/>
       <c r="J35" s="50"/>
     </row>
     <row r="36" spans="1:10" s="23" customFormat="1">
-      <c r="A36" s="72"/>
+      <c r="A36" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modela la organización y utiliza herramientas de inteligencia de negocios.</t>
+        </is>
+      </c>
       <c r="B36" s="73"/>
-      <c r="C36" s="43"/>
+      <c r="C36" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Aplicar</t>
+        </is>
+      </c>
       <c r="D36" s="43"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="79"/>
+      <c r="F36" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA02</t>
+        </is>
+      </c>
+      <c r="G36" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Construir modelos de la empresa como sistema dinámico para apoyar el proceso de toma de decisiones.</t>
+        </is>
+      </c>
       <c r="H36" s="80"/>
       <c r="I36" s="81"/>
       <c r="J36" s="50"/>
@@ -2612,11 +2644,23 @@
     <row r="37" spans="1:10" s="23" customFormat="1">
       <c r="A37" s="72"/>
       <c r="B37" s="73"/>
-      <c r="C37" s="43"/>
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Aplicar</t>
+        </is>
+      </c>
       <c r="D37" s="43"/>
       <c r="E37" s="43"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="79"/>
+      <c r="F37" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA03</t>
+        </is>
+      </c>
+      <c r="G37" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diseñar soluciones de almacenamiento y procesamiento analítico de datos (almacenes de datos, procesamiento analítico en línea y minería de datos) con herramientas de software de inteligencia de negocios.</t>
+        </is>
+      </c>
       <c r="H37" s="80"/>
       <c r="I37" s="81"/>
       <c r="J37" s="50"/>
@@ -2624,23 +2668,51 @@
     <row r="38" spans="1:10" s="23" customFormat="1">
       <c r="A38" s="72"/>
       <c r="B38" s="73"/>
-      <c r="C38" s="43"/>
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Analizar</t>
+        </is>
+      </c>
       <c r="D38" s="43"/>
       <c r="E38" s="43"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="69"/>
+      <c r="F38" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA04</t>
+        </is>
+      </c>
+      <c r="G38" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analizar información empresarial mediante técnicas estadísticas descriptivas y multivariadas y de inteligencia retrospectiva y prospectiva.</t>
+        </is>
+      </c>
       <c r="H38" s="70"/>
       <c r="I38" s="71"/>
       <c r="J38" s="50"/>
     </row>
     <row r="39" spans="1:10" s="23" customFormat="1">
-      <c r="A39" s="72"/>
+      <c r="A39" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diseña estrategias de inteligencia de negocios que aportan valor a la organización.</t>
+        </is>
+      </c>
       <c r="B39" s="73"/>
-      <c r="C39" s="43"/>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Crear</t>
+        </is>
+      </c>
       <c r="D39" s="43"/>
       <c r="E39" s="43"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="82"/>
+      <c r="F39" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA05</t>
+        </is>
+      </c>
+      <c r="G39" s="82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diseñar una estrategia de inteligencia integral de negocios que articule la planeación, el presupuesto y la toma de decisiones de una organización.</t>
+        </is>
+      </c>
       <c r="H39" s="83"/>
       <c r="I39" s="84"/>
       <c r="J39" s="50"/>
@@ -2899,7 +2971,11 @@
       <c r="C57" s="46"/>
       <c r="D57" s="37"/>
       <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
+      <c r="F57" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G57" s="37"/>
       <c r="H57" s="37"/>
       <c r="I57" s="37"/>
@@ -2912,7 +2988,11 @@
       <c r="B58" s="46"/>
       <c r="C58" s="46"/>
       <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
+      <c r="E58" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="F58" s="37"/>
       <c r="G58" s="37"/>
       <c r="H58" s="38"/>
@@ -2926,9 +3006,17 @@
       <c r="B59" s="46"/>
       <c r="C59" s="46"/>
       <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
+      <c r="E59" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
+      <c r="G59" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="H59" s="37"/>
       <c r="I59" s="38"/>
       <c r="J59" s="58"/>
@@ -2940,8 +3028,16 @@
       <c r="B60" s="46"/>
       <c r="C60" s="46"/>
       <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
+      <c r="E60" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="F60" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G60" s="37"/>
       <c r="H60" s="37"/>
       <c r="I60" s="37"/>
@@ -2957,8 +3053,16 @@
       <c r="E61" s="38"/>
       <c r="F61" s="37"/>
       <c r="G61" s="37"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="37"/>
+      <c r="H61" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="I61" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="J61" s="58"/>
     </row>
     <row r="62" spans="1:10">
@@ -3024,11 +3128,31 @@
       <c r="B66" s="46"/>
       <c r="C66" s="46"/>
       <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="38"/>
-      <c r="I66" s="38"/>
+      <c r="E66" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHP</t>
+        </is>
+      </c>
+      <c r="F66" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EE</t>
+        </is>
+      </c>
+      <c r="G66" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EBP</t>
+        </is>
+      </c>
+      <c r="H66" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EBP</t>
+        </is>
+      </c>
+      <c r="I66" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EOP</t>
+        </is>
+      </c>
       <c r="J66" s="58"/>
     </row>
     <row r="67" spans="1:10">
@@ -3038,11 +3162,31 @@
       <c r="B67" s="46"/>
       <c r="C67" s="46"/>
       <c r="D67" s="38"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="38"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38"/>
+      <c r="E67" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30%</t>
+        </is>
+      </c>
+      <c r="F67" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20%</t>
+        </is>
+      </c>
+      <c r="G67" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10%</t>
+        </is>
+      </c>
+      <c r="H67" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30%</t>
+        </is>
+      </c>
+      <c r="I67" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10%</t>
+        </is>
+      </c>
       <c r="J67" s="58"/>
     </row>
     <row r="68" spans="1:10">
@@ -3052,11 +3196,31 @@
       <c r="B68" s="46"/>
       <c r="C68" s="46"/>
       <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
-      <c r="H68" s="16"/>
-      <c r="I68" s="16"/>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="H68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
       <c r="J68" s="58"/>
     </row>
     <row r="69" spans="1:10">
